--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -436,16 +436,16 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -559,20 +559,16 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C2" t="n">
+        <v>3645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>114567</t>
-        </is>
+      <c r="E2" t="n">
+        <v>114567</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -581,7 +577,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:06:53</t>
+          <t>2026-09-12 8:06:53</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -591,19 +587,41 @@
         <v>67.146399</v>
       </c>
       <c r="J2" t="n">
-        <v>20.89999961853027</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>20.89999962</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:07:25</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>24.9450618</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67.14640489999999</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>00:00:32</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0089</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -436,11 +436,11 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:07:25</t>
+          <t>2026-09-12 8:07:25</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>00:00:32</t>
+          <t>0:00:32</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -625,8 +625,67 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIS-20260912082054-319FF8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>112345</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ammar ps</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:20:54</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24.9454852</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67.1463851</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.76199913024902</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S2"/>
+  <autoFilter ref="A1:S3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -440,10 +440,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -670,17 +670,39 @@
       <c r="J3" t="n">
         <v>21.76199913024902</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:21:16</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>24.9454799</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67.14637209999999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>45.59999847412109</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>00:00:22</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0061</v>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,15 +435,15 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -636,20 +636,16 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C3" t="n">
+        <v>3645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>112345</t>
-        </is>
+      <c r="E3" t="n">
+        <v>112345</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -658,7 +654,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-12 08:20:54</t>
+          <t>2026-09-12 8:20:54</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -668,11 +664,11 @@
         <v>67.1463851</v>
       </c>
       <c r="J3" t="n">
-        <v>21.76199913024902</v>
+        <v>21.76199913</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-12 08:21:16</t>
+          <t>2026-09-12 8:21:16</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -682,7 +678,7 @@
         <v>67.14637209999999</v>
       </c>
       <c r="N3" t="n">
-        <v>45.59999847412109</v>
+        <v>45.59999847</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
@@ -694,7 +690,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>00:00:22</t>
+          <t>0:00:22</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -706,8 +702,67 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VIS-20260912083421-874DFB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>117865</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ammar petroleum</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:34:21</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>24.9454157</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.1463612</v>
+      </c>
+      <c r="J4" t="n">
+        <v>45.59999847412109</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S3"/>
+  <autoFilter ref="A1:S4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -436,14 +436,14 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -713,20 +713,16 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C4" t="n">
+        <v>3645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>117865</t>
-        </is>
+      <c r="E4" t="n">
+        <v>117865</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -735,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-12 08:34:21</t>
+          <t>2026-09-12 8:34:21</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -745,19 +741,41 @@
         <v>67.1463612</v>
       </c>
       <c r="J4" t="n">
-        <v>45.59999847412109</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+        <v>45.59999847</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-12 14:58:33</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>24.9450655</v>
+      </c>
+      <c r="M4" t="n">
+        <v>67.1463991</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20.39999961853027</v>
+      </c>
+      <c r="O4" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>06:24:12</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>6.4033</v>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -436,14 +436,14 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -755,7 +755,7 @@
         <v>67.1463991</v>
       </c>
       <c r="N4" t="n">
-        <v>20.39999961853027</v>
+        <v>20.39999962</v>
       </c>
       <c r="O4" t="n">
         <v>39.1</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>06:24:12</t>
+          <t>6:24:12</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -779,8 +779,67 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VIS-20260912150702-A5A281</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Manesh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3333</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:07:02</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>24.8274653</v>
+      </c>
+      <c r="I5" t="n">
+        <v>67.0425759</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.25299835205078</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -443,9 +443,9 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -824,17 +824,39 @@
       <c r="J5" t="n">
         <v>33.25299835205078</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:07:26</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>24.8263333</v>
+      </c>
+      <c r="M5" t="n">
+        <v>67.0432167</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9.699999809265137</v>
+      </c>
+      <c r="O5" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Some Difference</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>00:00:24</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0067</v>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -790,25 +790,19 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="C5" t="n">
+        <v>222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Manesh</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3333</t>
-        </is>
+      <c r="E5" t="n">
+        <v>333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3333</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -822,7 +816,7 @@
         <v>67.0425759</v>
       </c>
       <c r="J5" t="n">
-        <v>33.25299835205078</v>
+        <v>33.25299835</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -836,7 +830,7 @@
         <v>67.0432167</v>
       </c>
       <c r="N5" t="n">
-        <v>9.699999809265137</v>
+        <v>9.699999808999999</v>
       </c>
       <c r="O5" t="n">
         <v>141.5</v>
@@ -848,7 +842,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>00:00:24</t>
+          <t>0:00:24</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -860,8 +854,67 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VIS-20260912151809-FFE01B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Zubair</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>101709</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Qurban</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:18:09</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>24.9072354</v>
+      </c>
+      <c r="I6" t="n">
+        <v>67.1118646</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.04999923706055</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -443,7 +443,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -899,17 +899,39 @@
       <c r="J6" t="n">
         <v>16.04999923706055</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:18:23</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>24.9072451</v>
+      </c>
+      <c r="M6" t="n">
+        <v>67.11186600000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.11200046539307</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>00:00:14</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0039</v>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -443,7 +443,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -865,20 +865,16 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2626</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Zubair</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
+      <c r="E6" t="n">
+        <v>101709</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -897,7 +893,7 @@
         <v>67.1118646</v>
       </c>
       <c r="J6" t="n">
-        <v>16.04999923706055</v>
+        <v>16.04999924</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -911,7 +907,7 @@
         <v>67.11186600000001</v>
       </c>
       <c r="N6" t="n">
-        <v>15.11200046539307</v>
+        <v>15.11200047</v>
       </c>
       <c r="O6" t="n">
         <v>1.1</v>
@@ -923,7 +919,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>00:00:14</t>
+          <t>0:00:14</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -935,8 +931,67 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VIS-20260912151930-615F95</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mamesh</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Manesh</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:19:30</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>24.8256526</v>
+      </c>
+      <c r="I7" t="n">
+        <v>67.03676539999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.88999938964844</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -942,20 +942,16 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Mamesh</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
+      <c r="E7" t="n">
+        <v>1234</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -974,7 +970,7 @@
         <v>67.03676539999999</v>
       </c>
       <c r="J7" t="n">
-        <v>17.88999938964844</v>
+        <v>17.88999939</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -990,8 +986,67 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VIS-20260912160123-EBFDCB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>44582</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Macca</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-12 16:01:23</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>24.9456592</v>
+      </c>
+      <c r="I8" t="n">
+        <v>67.14645419999999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>52.40000152587891</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-09-12.xlsx
+++ b/data/visits/Visits_2026-09-12.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$S$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -997,20 +997,16 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3635</t>
-        </is>
+      <c r="C8" t="n">
+        <v>3635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>44582</t>
-        </is>
+      <c r="E8" t="n">
+        <v>44582</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1029,7 +1025,7 @@
         <v>67.14645419999999</v>
       </c>
       <c r="J8" t="n">
-        <v>52.40000152587891</v>
+        <v>52.40000153</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1045,8 +1041,67 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VIS-20260912231758-C4FCC1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>116152</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Karachi Gasoline</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-12 23:17:58</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>24.9450622</v>
+      </c>
+      <c r="I9" t="n">
+        <v>67.14640129999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>